--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/TEXAS_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/TEXAS_2021.xlsx
@@ -517,7 +517,7 @@
         <v>135</v>
       </c>
       <c r="D9">
-        <v>0.0009660038210817811</v>
+        <v>0.0009660038210817812</v>
       </c>
     </row>
     <row r="10">
@@ -661,7 +661,7 @@
         <v>133</v>
       </c>
       <c r="D17">
-        <v>0.0009516926533620511</v>
+        <v>0.0009516926533620512</v>
       </c>
     </row>
     <row r="18">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C190">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C254">
@@ -5503,7 +5503,7 @@
         <v>135</v>
       </c>
       <c r="D286">
-        <v>0.0009660038210817811</v>
+        <v>0.0009660038210817812</v>
       </c>
     </row>
     <row r="287">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C408">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C418">
@@ -8185,7 +8185,7 @@
         <v>1276</v>
       </c>
       <c r="D435">
-        <v>0.009130525005187799</v>
+        <v>0.0091305250051878</v>
       </c>
     </row>
     <row r="436">
@@ -8203,7 +8203,7 @@
         <v>134</v>
       </c>
       <c r="D436">
-        <v>0.0009588482372219161</v>
+        <v>0.000958848237221916</v>
       </c>
     </row>
     <row r="437">
@@ -9085,7 +9085,7 @@
         <v>138</v>
       </c>
       <c r="D485">
-        <v>0.0009874705726613763</v>
+        <v>0.0009874705726613765</v>
       </c>
     </row>
     <row r="486">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C914">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C916">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C917">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1084">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1133">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1687">
@@ -31675,7 +31675,7 @@
         <v>133</v>
       </c>
       <c r="D1740">
-        <v>0.0009516926533620511</v>
+        <v>0.0009516926533620512</v>
       </c>
     </row>
     <row r="1741">
@@ -34087,7 +34087,7 @@
         <v>129</v>
       </c>
       <c r="D1874">
-        <v>0.0009230703179225909</v>
+        <v>0.0009230703179225908</v>
       </c>
     </row>
     <row r="1875">
